--- a/data/trans_orig/P25F_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023</t>
+          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023 (tasa de respuesta: 90,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3177</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2381</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26100</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>32827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -1751,97 +1751,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2990</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>699</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>21,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1696</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2488</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6714</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1696</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6289</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5887</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84055</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25F_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Habitat-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>666</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25436</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>31554</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>31554</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>31554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
